--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104545_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104545_W10.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4543</v>
+        <v>10.9925</v>
       </c>
       <c r="E2" t="n">
-        <v>8.088100000000001</v>
+        <v>8.4687</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3662</v>
+        <v>2.5238</v>
       </c>
       <c r="G2" t="n">
-        <v>8.0745</v>
+        <v>8.061</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5223</v>
+        <v>2.5217</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5522</v>
+        <v>5.5393</v>
       </c>
       <c r="J2" t="n">
-        <v>8.0389</v>
+        <v>7.9998</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0363</v>
+        <v>2.02</v>
       </c>
       <c r="L2" t="n">
-        <v>6.0026</v>
+        <v>5.9798</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0356</v>
+        <v>0.0613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.208</v>
+        <v>-0.6619</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0434</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1645</v>
+        <v>-0.0414</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5265</v>
+        <v>5.1956</v>
       </c>
       <c r="E3" t="n">
-        <v>5.078</v>
+        <v>5.4951</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5515</v>
+        <v>-0.2995</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2515</v>
+        <v>2.2294</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0161</v>
+        <v>3.9962</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7646</v>
+        <v>-1.7668</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8581</v>
+        <v>3.8171</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6396</v>
+        <v>3.609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6066</v>
+        <v>-1.5877</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9518</v>
+        <v>-0.2614</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4134</v>
+        <v>-0.1961</v>
       </c>
       <c r="V3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4362</v>
+        <v>2.8724</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2031</v>
+        <v>1.6337</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2331</v>
+        <v>1.2387</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1259</v>
+        <v>2.1195</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6132</v>
+        <v>3.6076</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4874</v>
+        <v>-1.4882</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1489</v>
+        <v>2.1147</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1272</v>
+        <v>3.1059</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9784</v>
+        <v>-0.9912</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N4" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7558</v>
+        <v>-0.317</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1485</v>
+        <v>0.1154</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3686</v>
+        <v>1.1704</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4511</v>
+        <v>1.4964</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0825</v>
+        <v>-0.326</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0632</v>
+        <v>-1.0535</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1412</v>
+        <v>1.1512</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2044</v>
+        <v>-2.2046</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5684</v>
+        <v>-0.5845</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9697</v>
+        <v>0.9653</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5381</v>
+        <v>-1.5497</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4948</v>
+        <v>-0.469</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0027</v>
+        <v>-0.2102</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3266</v>
+        <v>-0.2559</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3293</v>
+        <v>0.0457</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0226</v>
+        <v>0.9285</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1752</v>
+        <v>-0.3683</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1978</v>
+        <v>1.2968</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4494</v>
+        <v>1.4501</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5396</v>
+        <v>2.539</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0902</v>
+        <v>-1.0888</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2675</v>
+        <v>1.2441</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5341</v>
+        <v>1.5201</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M6" t="n">
-        <v>0.182</v>
+        <v>0.206</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0055</v>
+        <v>1.0189</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6025</v>
+        <v>-0.7085</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3085</v>
+        <v>-0.4743</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.294</v>
+        <v>-0.2342</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6598000000000001</v>
+        <v>-0.1617</v>
       </c>
       <c r="E7" t="n">
-        <v>1.199</v>
+        <v>0.4232</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5391</v>
+        <v>-0.5849</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2449</v>
+        <v>0.2426</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5354</v>
+        <v>0.5315</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2905</v>
+        <v>-0.2889</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2707</v>
+        <v>1.2596</v>
       </c>
       <c r="K7" t="n">
-        <v>0.599</v>
+        <v>0.5893</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0258</v>
+        <v>-1.0169</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0955</v>
+        <v>0.2786</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1039</v>
+        <v>0.3505</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3972</v>
+        <v>-0.3327</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0449</v>
+        <v>-1.0492</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.7165</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4571</v>
+        <v>-0.4558</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4358</v>
+        <v>-0.4365</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7007</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24</v>
+        <v>0.2449</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6206</v>
+        <v>-0.5598</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4169</v>
+        <v>-1.31</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7068</v>
+        <v>-1.4836</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2899</v>
+        <v>0.1736</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3152</v>
+        <v>-1.3192</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9394</v>
+        <v>-0.9392</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3759</v>
+        <v>-0.38</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3639</v>
+        <v>-0.3732</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9513</v>
+        <v>-0.946</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1016</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1071</v>
+        <v>-0.0185</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6709</v>
+        <v>-1.7254</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4913</v>
+        <v>-1.3152</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8204</v>
+        <v>-0.4101</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5519</v>
+        <v>-3.697</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1963</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7481</v>
+        <v>-4.4605</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3584</v>
+        <v>-2.0499</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5053</v>
+        <v>0.7067</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8637</v>
+        <v>-2.7566</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1935</v>
+        <v>-1.6471</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.0568</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8844</v>
+        <v>-1.7039</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1739</v>
+        <v>0.0823</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1089</v>
+        <v>0.0322</v>
       </c>
       <c r="U10" t="n">
-        <v>0.065</v>
+        <v>0.0501</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6268</v>
+        <v>-1.9516</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1088</v>
+        <v>-3.6467</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.518</v>
+        <v>1.6951</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1229</v>
+        <v>-1.5531</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0491</v>
+        <v>1.1921</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0738</v>
+        <v>-2.7452</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2045</v>
+        <v>-0.3826</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8485</v>
+        <v>0.4891</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.053</v>
+        <v>-0.8718</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9185</v>
+        <v>-1.1704</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8976</v>
+        <v>0.703</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0209</v>
+        <v>-1.8734</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>2.9592</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1352</v>
+        <v>-0.101</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2299</v>
+        <v>-0.0073</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6534</v>
+        <v>-2.461</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9981</v>
+        <v>-1.0575</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6554</v>
+        <v>-1.4036</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6902</v>
+        <v>-2.1274</v>
       </c>
       <c r="H12" t="n">
-        <v>0.756</v>
+        <v>-0.0461</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4462</v>
+        <v>-2.0813</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0277</v>
+        <v>-0.221</v>
       </c>
       <c r="K12" t="n">
-        <v>0.71</v>
+        <v>0.8446</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7377</v>
+        <v>-1.0656</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6626</v>
+        <v>-1.9064</v>
       </c>
       <c r="N12" t="n">
-        <v>0.046</v>
+        <v>-0.8907</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7086</v>
+        <v>-1.0157</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8459</v>
+        <v>0.3006</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6775</v>
+        <v>0.3017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1685</v>
+        <v>-0.0011</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3437</v>
+        <v>-4.5129</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8227</v>
+        <v>-1.9011</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.521</v>
+        <v>-2.6118</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0302</v>
+        <v>-3.0223</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5988</v>
+        <v>-1.597</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4313</v>
+        <v>-1.4253</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4481</v>
+        <v>-0.4581</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L13" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5821</v>
+        <v>-2.5642</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1404</v>
+        <v>-2.1328</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0306</v>
+        <v>0.8476</v>
       </c>
       <c r="T13" t="n">
-        <v>1.733</v>
+        <v>0.6756</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2976</v>
+        <v>0.1721</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.359100000000005</v>
+        <v>8.704099999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>6.671499999999998</v>
+        <v>6.695499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.687600000000001</v>
+        <v>2.008599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9155000000000015</v>
+        <v>0.8743000000000007</v>
       </c>
       <c r="H14" t="n">
-        <v>13.297</v>
+        <v>13.2841</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.3815</v>
+        <v>-12.4096</v>
       </c>
       <c r="J14" t="n">
-        <v>11.916</v>
+        <v>11.6653</v>
       </c>
       <c r="K14" t="n">
-        <v>11.3438</v>
+        <v>11.2086</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5721000000000002</v>
+        <v>0.4566999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.0006</v>
+        <v>-10.7907</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9531</v>
+        <v>2.0756</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.9538</v>
+        <v>-12.8664</v>
       </c>
       <c r="P14" t="n">
-        <v>11.3416</v>
+        <v>11.3815</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R14" t="n">
-        <v>24.9516</v>
+        <v>25.0394</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.648299999999999</v>
+        <v>-1.3014</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.179400000000001</v>
+        <v>-0.8164</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4688999999999999</v>
+        <v>-0.4848999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.2496</v>
+        <v>-2.2503</v>
       </c>
       <c r="W14" t="n">
-        <v>9.545100000000001</v>
+        <v>9.5047</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.7946</v>
+        <v>-11.755</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.54</v>
+        <v>4.6578</v>
       </c>
       <c r="E15" t="n">
-        <v>7.4035</v>
+        <v>7.3431</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8635</v>
+        <v>-2.6853</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8441</v>
+        <v>4.8341</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.9236</v>
+        <v>-1.9161</v>
       </c>
       <c r="I15" t="n">
-        <v>6.7676</v>
+        <v>6.7502</v>
       </c>
       <c r="J15" t="n">
-        <v>7.4437</v>
+        <v>7.3992</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7375</v>
+        <v>0.7272</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7062</v>
+        <v>6.672</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5996</v>
+        <v>-2.5651</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6611</v>
+        <v>-2.6433</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0614</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3702</v>
+        <v>-0.2462</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1179</v>
+        <v>-0.1165</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2523</v>
+        <v>-0.1297</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2384</v>
+        <v>3.8875</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5887</v>
+        <v>3.7966</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3503</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3266</v>
+        <v>0.3335</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0377</v>
+        <v>-2.0228</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3643</v>
+        <v>2.3562</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6604</v>
+        <v>1.6367</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3428</v>
+        <v>2.3229</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3338</v>
+        <v>-1.3032</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3552</v>
+        <v>-1.3365</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.046</v>
+        <v>0.6922</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2571</v>
+        <v>-0.019</v>
       </c>
       <c r="U16" t="n">
-        <v>0.303</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9031</v>
+        <v>1.8727</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.4101</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3401</v>
+        <v>1.4625</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8321</v>
+        <v>0.8329</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2109</v>
+        <v>0.1961</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6212</v>
+        <v>0.6368</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8233</v>
+        <v>0.7992</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6367</v>
+        <v>0.613</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3393</v>
+        <v>0.3161</v>
       </c>
       <c r="T17" t="n">
-        <v>0.369</v>
+        <v>0.253</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0297</v>
+        <v>0.0631</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8518</v>
+        <v>1.5706</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.207</v>
+        <v>3.4244</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0589</v>
+        <v>-1.8538</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6646</v>
+        <v>0.9666</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9695</v>
+        <v>-0.7244</v>
       </c>
       <c r="I18" t="n">
-        <v>1.634</v>
+        <v>1.691</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7057</v>
+        <v>2.37</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3699</v>
+        <v>0.3964</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3359</v>
+        <v>1.9736</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0411</v>
+        <v>-1.4034</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3393</v>
+        <v>-1.1209</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2982</v>
+        <v>-0.2826</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0227</v>
+        <v>0.2579</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.0351</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.2929</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0246</v>
+        <v>-1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6999</v>
+        <v>0.8797</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8427</v>
+        <v>-0.9016</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1428</v>
+        <v>1.7812</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9486</v>
+        <v>0.6619</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7361</v>
+        <v>-0.9816</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6847</v>
+        <v>1.6435</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3761</v>
+        <v>0.6756</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3983</v>
+        <v>0.3405</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9778</v>
+        <v>0.3351</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4275</v>
+        <v>-0.0138</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1344</v>
+        <v>-1.3221</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2931</v>
+        <v>1.3083</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5831</v>
+        <v>0.0177</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6261</v>
+        <v>-0.3417</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0429</v>
+        <v>0.3594</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>2.0212</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1996,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6835</v>
+        <v>-2.4227</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9337</v>
+        <v>-2.7171</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2502</v>
+        <v>0.2944</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0984</v>
+        <v>-1.1</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5627</v>
+        <v>-0.5684</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5357</v>
+        <v>-0.5316</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3871</v>
+        <v>-0.3989</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4991</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7113</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2241</v>
+        <v>0.043</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2782</v>
+        <v>-0.0419</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6657</v>
+        <v>-5.2411</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1566</v>
+        <v>-3.0744</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5091</v>
+        <v>-2.1666</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.361</v>
+        <v>-0.348</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5079</v>
+        <v>0.5111</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8689</v>
+        <v>-0.8591</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5492</v>
+        <v>1.5424</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9103</v>
+        <v>-1.8904</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P22" t="n">
-        <v>-5.444</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5249</v>
+        <v>0.9571</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>0.4202</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2255</v>
+        <v>0.5369</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.443</v>
+        <v>-5.5021</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1325</v>
+        <v>-5.8957</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3105</v>
+        <v>0.3935</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.2102</v>
+        <v>-5.2153</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.802</v>
+        <v>-5.8098</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5918</v>
+        <v>0.5945</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.5224</v>
+        <v>-3.5689</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.7382</v>
+        <v>-3.7693</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2158</v>
+        <v>0.2004</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6878</v>
+        <v>-1.6464</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0638</v>
+        <v>-2.0405</v>
       </c>
       <c r="O23" t="n">
-        <v>0.376</v>
+        <v>0.3941</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5819</v>
+        <v>0.5342</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2461</v>
+        <v>0.543</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6642</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6271</v>
+        <v>-7.0958</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5631</v>
+        <v>-3.3045</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.064</v>
+        <v>-3.7912</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6885</v>
+        <v>-1.6675</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1227</v>
+        <v>0.1284</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3516</v>
+        <v>0.3355</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0401</v>
+        <v>-2.0031</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.198</v>
+        <v>-1.1786</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8245</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3563</v>
+        <v>-0.1323</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5293</v>
+        <v>-0.1769</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.173</v>
+        <v>0.0446</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.359299999999999</v>
+        <v>-7.565799999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5950000000000002</v>
+        <v>-0.9190999999999994</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.7642</v>
+        <v>-6.646899999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9153000000000007</v>
+        <v>-0.8741999999999996</v>
       </c>
       <c r="H25" t="n">
-        <v>-13.2972</v>
+        <v>-13.2842</v>
       </c>
       <c r="I25" t="n">
-        <v>12.3817</v>
+        <v>12.4099</v>
       </c>
       <c r="J25" t="n">
-        <v>11.0005</v>
+        <v>10.7908</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.9533</v>
+        <v>-2.0756</v>
       </c>
       <c r="L25" t="n">
-        <v>12.9539</v>
+        <v>12.8664</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.9159</v>
+        <v>-11.6653</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.3438</v>
+        <v>-11.2086</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5722</v>
+        <v>-0.4567000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="Q25" t="n">
-        <v>-24.9516</v>
+        <v>-25.0394</v>
       </c>
       <c r="R25" t="n">
-        <v>13.6099</v>
+        <v>13.6578</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6483</v>
+        <v>2.4397</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4689</v>
+        <v>0.4851</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1792</v>
+        <v>1.9545</v>
       </c>
       <c r="V25" t="n">
-        <v>2.2494</v>
+        <v>2.2503</v>
       </c>
       <c r="W25" t="n">
-        <v>12.8871</v>
+        <v>12.8444</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.6376</v>
+        <v>-10.5941</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104545_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104545_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.755</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104545_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-10.5941</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
